--- a/informes_data/Segunda FEB/2026-27/Regular_Season/aggregate_individual/AGG_IND_SOL GIRONÈS BISBAL BÀSQUET.xlsx
+++ b/informes_data/Segunda FEB/2026-27/Regular_Season/aggregate_individual/AGG_IND_SOL GIRONÈS BISBAL BÀSQUET.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X15"/>
+  <dimension ref="A1:X14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -697,7 +697,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>X. TORRENT BAYÉ</t>
+          <t>I. VALERA COROMINAS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -709,73 +709,73 @@
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>1.759</v>
+        <v>-1.0899</v>
       </c>
       <c r="E4" t="n">
-        <v>1.759</v>
+        <v>0.1051</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>-1.195</v>
       </c>
       <c r="G4" t="n">
-        <v>1.759</v>
+        <v>1.5332</v>
       </c>
       <c r="H4" t="n">
-        <v>1.1672</v>
+        <v>1.1786</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5918</v>
+        <v>0.3545</v>
       </c>
       <c r="J4" t="n">
-        <v>1.759</v>
+        <v>1.3233</v>
       </c>
       <c r="K4" t="n">
-        <v>1.1672</v>
+        <v>1.2838</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5918</v>
+        <v>0.0395</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>0.2098</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>-0.1052</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>0.3150000000000001</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>-0.2055</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-1.0274</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>0.8219</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>-0.06129999999999999</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>-0.1907</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>0.1294</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>-2.3561</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-2.3561</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>I. VALERA COROMINAS</t>
+          <t>B. ALVAREZ TORRES</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -784,76 +784,76 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.0899</v>
+        <v>-1.2255</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1051</v>
+        <v>-2.1362</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.195</v>
+        <v>0.9106</v>
       </c>
       <c r="G5" t="n">
-        <v>1.5332</v>
+        <v>2.0394</v>
       </c>
       <c r="H5" t="n">
-        <v>1.1786</v>
+        <v>-4.512</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3545</v>
+        <v>6.5514</v>
       </c>
       <c r="J5" t="n">
-        <v>1.3233</v>
+        <v>4.341</v>
       </c>
       <c r="K5" t="n">
-        <v>1.2838</v>
+        <v>-0.7941000000000003</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0395</v>
+        <v>5.1351</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2098</v>
+        <v>-2.3016</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.1052</v>
+        <v>-3.7179</v>
       </c>
       <c r="O5" t="n">
-        <v>0.3150000000000001</v>
+        <v>1.4164</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.2055</v>
+        <v>2.220446049250313e-16</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.0274</v>
+        <v>-5.548</v>
       </c>
       <c r="R5" t="n">
-        <v>0.8219</v>
+        <v>5.548</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.06129999999999999</v>
+        <v>-1.9251</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1907</v>
+        <v>-1.7578</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1294</v>
+        <v>-0.1673</v>
       </c>
       <c r="V5" t="n">
-        <v>-2.3561</v>
+        <v>-1.3397</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.8288</v>
       </c>
       <c r="X5" t="n">
-        <v>-2.3561</v>
+        <v>-2.1684</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>B. ALVAREZ TORRES</t>
+          <t>A. DOMINGUEZ ESPELT</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -865,73 +865,73 @@
         <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.2255</v>
+        <v>-2.1676</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.1362</v>
+        <v>1.5515</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9106</v>
+        <v>-3.7191</v>
       </c>
       <c r="G6" t="n">
-        <v>2.0394</v>
+        <v>-0.8448000000000002</v>
       </c>
       <c r="H6" t="n">
-        <v>-4.512</v>
+        <v>-0.1786000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>6.5514</v>
+        <v>-0.6661</v>
       </c>
       <c r="J6" t="n">
-        <v>4.341</v>
+        <v>7.799799999999999</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.7941000000000003</v>
+        <v>5.8576</v>
       </c>
       <c r="L6" t="n">
-        <v>5.1351</v>
+        <v>1.9422</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.3016</v>
+        <v>-8.644600000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>-3.7179</v>
+        <v>-6.0363</v>
       </c>
       <c r="O6" t="n">
-        <v>1.4164</v>
+        <v>-2.6084</v>
       </c>
       <c r="P6" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>-2.8768</v>
       </c>
       <c r="Q6" t="n">
-        <v>-5.548</v>
+        <v>-10.274</v>
       </c>
       <c r="R6" t="n">
-        <v>5.548</v>
+        <v>7.3973</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.9251</v>
+        <v>-1.2816</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.7578</v>
+        <v>-0.4673999999999999</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1673</v>
+        <v>-0.8143</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.3397</v>
+        <v>2.8356</v>
       </c>
       <c r="W6" t="n">
-        <v>0.8288</v>
+        <v>4.4931</v>
       </c>
       <c r="X6" t="n">
-        <v>-2.1684</v>
+        <v>-1.6575</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. DOMINGUEZ ESPELT</t>
+          <t>J. LAFUENTE VELAZQUEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -943,73 +943,73 @@
         <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.1676</v>
+        <v>-4.961000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>1.5515</v>
+        <v>-1.6801</v>
       </c>
       <c r="F7" t="n">
-        <v>-3.7191</v>
+        <v>-3.2806</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.8448000000000002</v>
+        <v>1.162</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.1786000000000001</v>
+        <v>-3.7572</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.6661</v>
+        <v>4.9193</v>
       </c>
       <c r="J7" t="n">
-        <v>7.799799999999999</v>
+        <v>10.6696</v>
       </c>
       <c r="K7" t="n">
-        <v>5.8576</v>
+        <v>3.8829</v>
       </c>
       <c r="L7" t="n">
-        <v>1.9422</v>
+        <v>6.786899999999999</v>
       </c>
       <c r="M7" t="n">
-        <v>-8.644600000000001</v>
+        <v>-9.5077</v>
       </c>
       <c r="N7" t="n">
-        <v>-6.0363</v>
+        <v>-7.64</v>
       </c>
       <c r="O7" t="n">
-        <v>-2.6084</v>
+        <v>-1.8677</v>
       </c>
       <c r="P7" t="n">
-        <v>-2.8768</v>
+        <v>-3.0821</v>
       </c>
       <c r="Q7" t="n">
-        <v>-10.274</v>
+        <v>-11.7124</v>
       </c>
       <c r="R7" t="n">
-        <v>7.3973</v>
+        <v>8.6303</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.2816</v>
+        <v>-1.2214</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4673999999999999</v>
+        <v>-0.6375</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.8143</v>
+        <v>-0.5841000000000001</v>
       </c>
       <c r="V7" t="n">
-        <v>2.8356</v>
+        <v>-1.8192</v>
       </c>
       <c r="W7" t="n">
-        <v>4.4931</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.6575</v>
+        <v>-1.8192</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. LAFUENTE VELAZQUEZ</t>
+          <t>B. SAGNA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1021,73 +1021,73 @@
         <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>-4.961000000000001</v>
+        <v>-5.5755</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.6801</v>
+        <v>-4.9021</v>
       </c>
       <c r="F8" t="n">
-        <v>-3.2806</v>
+        <v>-0.6735000000000002</v>
       </c>
       <c r="G8" t="n">
-        <v>1.162</v>
+        <v>-3.749</v>
       </c>
       <c r="H8" t="n">
-        <v>-3.7572</v>
+        <v>-6.201999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>4.9193</v>
+        <v>2.453</v>
       </c>
       <c r="J8" t="n">
-        <v>10.6696</v>
+        <v>1.1193</v>
       </c>
       <c r="K8" t="n">
-        <v>3.8829</v>
+        <v>-1.2119</v>
       </c>
       <c r="L8" t="n">
-        <v>6.786899999999999</v>
+        <v>2.3311</v>
       </c>
       <c r="M8" t="n">
-        <v>-9.5077</v>
+        <v>-4.8683</v>
       </c>
       <c r="N8" t="n">
-        <v>-7.64</v>
+        <v>-4.9902</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.8677</v>
+        <v>0.122</v>
       </c>
       <c r="P8" t="n">
-        <v>-3.0821</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-11.7124</v>
+        <v>-5.548</v>
       </c>
       <c r="R8" t="n">
-        <v>8.6303</v>
+        <v>5.5481</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.2214</v>
+        <v>-1.7541</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.6375</v>
+        <v>-1.6514</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.5841000000000001</v>
+        <v>-0.1026000000000001</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.8192</v>
+        <v>-0.0726</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.1781</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.8192</v>
+        <v>-1.2507</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>B. SAGNA</t>
+          <t>M. MUKENDI MUKENDI</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1099,73 +1099,73 @@
         <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>-5.5755</v>
+        <v>-6.7499</v>
       </c>
       <c r="E9" t="n">
-        <v>-4.9021</v>
+        <v>-0.3836000000000002</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.6735000000000002</v>
+        <v>-6.366300000000001</v>
       </c>
       <c r="G9" t="n">
-        <v>-3.749</v>
+        <v>-3.0967</v>
       </c>
       <c r="H9" t="n">
-        <v>-6.201999999999999</v>
+        <v>-2.0292</v>
       </c>
       <c r="I9" t="n">
-        <v>2.453</v>
+        <v>-1.0674</v>
       </c>
       <c r="J9" t="n">
-        <v>1.1193</v>
+        <v>3.1594</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.2119</v>
+        <v>1.4623</v>
       </c>
       <c r="L9" t="n">
-        <v>2.3311</v>
+        <v>1.697</v>
       </c>
       <c r="M9" t="n">
-        <v>-4.8683</v>
+        <v>-6.2561</v>
       </c>
       <c r="N9" t="n">
-        <v>-4.9902</v>
+        <v>-3.4916</v>
       </c>
       <c r="O9" t="n">
-        <v>0.122</v>
+        <v>-2.7644</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.2328</v>
       </c>
       <c r="Q9" t="n">
-        <v>-5.548</v>
+        <v>-3.2877</v>
       </c>
       <c r="R9" t="n">
-        <v>5.5481</v>
+        <v>4.5205</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.7541</v>
+        <v>-1.7011</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.6514</v>
+        <v>-0.9744</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1026000000000001</v>
+        <v>-0.7268</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.0726</v>
+        <v>-3.1849</v>
       </c>
       <c r="W9" t="n">
-        <v>1.1781</v>
+        <v>0.7192</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.2507</v>
+        <v>-3.904</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. MUKENDI MUKENDI</t>
+          <t>J. LEEROY OSAGIE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1174,76 +1174,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>-6.7499</v>
+        <v>-6.8775</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.3836000000000002</v>
+        <v>-5.9852</v>
       </c>
       <c r="F10" t="n">
-        <v>-6.366300000000001</v>
+        <v>-0.8924000000000001</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.0967</v>
+        <v>-5.8122</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.0292</v>
+        <v>-6.3864</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.0674</v>
+        <v>0.5741000000000001</v>
       </c>
       <c r="J10" t="n">
-        <v>3.1594</v>
+        <v>-1.9612</v>
       </c>
       <c r="K10" t="n">
-        <v>1.4623</v>
+        <v>-3.4209</v>
       </c>
       <c r="L10" t="n">
-        <v>1.697</v>
+        <v>1.4598</v>
       </c>
       <c r="M10" t="n">
-        <v>-6.2561</v>
+        <v>-3.851</v>
       </c>
       <c r="N10" t="n">
-        <v>-3.4916</v>
+        <v>-2.9654</v>
       </c>
       <c r="O10" t="n">
-        <v>-2.7644</v>
+        <v>-0.8855000000000001</v>
       </c>
       <c r="P10" t="n">
-        <v>1.2328</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
         <v>-3.2877</v>
       </c>
       <c r="R10" t="n">
-        <v>4.5205</v>
+        <v>3.2877</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.7011</v>
+        <v>-1.1668</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.9744</v>
+        <v>-0.7363</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.7268</v>
+        <v>-0.4305</v>
       </c>
       <c r="V10" t="n">
-        <v>-3.1849</v>
+        <v>0.1014</v>
       </c>
       <c r="W10" t="n">
-        <v>0.7192</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-3.904</v>
+        <v>0.1014</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. LEEROY OSAGIE</t>
+          <t>O. FUENTES PELUFO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1252,76 +1252,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.8775</v>
+        <v>-8.120799999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.9852</v>
+        <v>-4.7896</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.8924000000000001</v>
+        <v>-3.3312</v>
       </c>
       <c r="G11" t="n">
-        <v>-5.8122</v>
+        <v>-6.1654</v>
       </c>
       <c r="H11" t="n">
-        <v>-6.3864</v>
+        <v>-5.3045</v>
       </c>
       <c r="I11" t="n">
-        <v>0.5741000000000001</v>
+        <v>-0.8609</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.9612</v>
+        <v>-1.4924</v>
       </c>
       <c r="K11" t="n">
-        <v>-3.4209</v>
+        <v>-0.8246</v>
       </c>
       <c r="L11" t="n">
-        <v>1.4598</v>
+        <v>-0.6678000000000002</v>
       </c>
       <c r="M11" t="n">
-        <v>-3.851</v>
+        <v>-4.6731</v>
       </c>
       <c r="N11" t="n">
-        <v>-2.9654</v>
+        <v>-4.48</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.8855000000000001</v>
+        <v>-0.1930000000000001</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>4.726</v>
       </c>
       <c r="Q11" t="n">
-        <v>-3.2877</v>
+        <v>-1.2329</v>
       </c>
       <c r="R11" t="n">
-        <v>3.2877</v>
+        <v>5.9589</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.1668</v>
+        <v>-0.5403</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7363</v>
+        <v>-0.6877</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.4305</v>
+        <v>0.1472</v>
       </c>
       <c r="V11" t="n">
-        <v>0.1014</v>
+        <v>-6.1411</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>-1.3767</v>
       </c>
       <c r="X11" t="n">
-        <v>0.1014</v>
+        <v>-4.7643</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>O. FUENTES PELUFO</t>
+          <t>M. RAGSDALE</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1333,73 +1333,73 @@
         <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>-8.120799999999999</v>
+        <v>-8.932400000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.7896</v>
+        <v>-3.080899999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.3312</v>
+        <v>-5.8513</v>
       </c>
       <c r="G12" t="n">
-        <v>-6.1654</v>
+        <v>-3.465</v>
       </c>
       <c r="H12" t="n">
-        <v>-5.3045</v>
+        <v>-4.2798</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.8609</v>
+        <v>0.8149</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.4924</v>
+        <v>7.5894</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.8246</v>
+        <v>3.3601</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.6678000000000002</v>
+        <v>4.229299999999999</v>
       </c>
       <c r="M12" t="n">
-        <v>-4.6731</v>
+        <v>-11.0546</v>
       </c>
       <c r="N12" t="n">
-        <v>-4.48</v>
+        <v>-7.6401</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.1930000000000001</v>
+        <v>-3.4145</v>
       </c>
       <c r="P12" t="n">
-        <v>4.726</v>
+        <v>1.2329</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.2329</v>
+        <v>-8.424700000000001</v>
       </c>
       <c r="R12" t="n">
-        <v>5.9589</v>
+        <v>9.6576</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.5403</v>
+        <v>-3.0564</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6877</v>
+        <v>-2.3759</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1472</v>
+        <v>-0.6805</v>
       </c>
       <c r="V12" t="n">
-        <v>-6.1411</v>
+        <v>-3.6439</v>
       </c>
       <c r="W12" t="n">
-        <v>-1.3767</v>
+        <v>0.1301</v>
       </c>
       <c r="X12" t="n">
-        <v>-4.7643</v>
+        <v>-3.774</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>M. RAGSDALE</t>
+          <t>X. TORRENT BAYE</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1411,73 +1411,73 @@
         <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>-8.932400000000001</v>
+        <v>-12.2323</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.080899999999999</v>
+        <v>-7.9029</v>
       </c>
       <c r="F13" t="n">
-        <v>-5.8513</v>
+        <v>-4.329499999999999</v>
       </c>
       <c r="G13" t="n">
-        <v>-3.465</v>
+        <v>-10.8955</v>
       </c>
       <c r="H13" t="n">
-        <v>-4.2798</v>
+        <v>-1.8921</v>
       </c>
       <c r="I13" t="n">
-        <v>0.8149</v>
+        <v>-9.003500000000001</v>
       </c>
       <c r="J13" t="n">
-        <v>7.5894</v>
+        <v>-5.228499999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>3.3601</v>
+        <v>1.5469</v>
       </c>
       <c r="L13" t="n">
-        <v>4.229299999999999</v>
+        <v>-6.7754</v>
       </c>
       <c r="M13" t="n">
-        <v>-11.0546</v>
+        <v>-5.667</v>
       </c>
       <c r="N13" t="n">
-        <v>-7.6401</v>
+        <v>-3.4389</v>
       </c>
       <c r="O13" t="n">
-        <v>-3.4145</v>
+        <v>-2.228</v>
       </c>
       <c r="P13" t="n">
-        <v>1.2329</v>
+        <v>1.6437</v>
       </c>
       <c r="Q13" t="n">
-        <v>-8.424700000000001</v>
+        <v>-3.0822</v>
       </c>
       <c r="R13" t="n">
-        <v>9.6576</v>
+        <v>4.726</v>
       </c>
       <c r="S13" t="n">
-        <v>-3.0564</v>
+        <v>-1.8024</v>
       </c>
       <c r="T13" t="n">
-        <v>-2.3759</v>
+        <v>-1.0098</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.6805</v>
+        <v>-0.7927</v>
       </c>
       <c r="V13" t="n">
-        <v>-3.6439</v>
+        <v>-1.1781</v>
       </c>
       <c r="W13" t="n">
-        <v>0.1301</v>
+        <v>1.4178</v>
       </c>
       <c r="X13" t="n">
-        <v>-3.774</v>
+        <v>-2.5959</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X. TORRENT BAYE</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1489,144 +1489,66 @@
         <v>4</v>
       </c>
       <c r="D14" t="n">
-        <v>-13.991</v>
+        <v>-52.6493</v>
       </c>
       <c r="E14" t="n">
-        <v>-9.6617</v>
+        <v>-28.5055</v>
       </c>
       <c r="F14" t="n">
-        <v>-4.329499999999999</v>
+        <v>-24.1436</v>
       </c>
       <c r="G14" t="n">
-        <v>-12.6545</v>
+        <v>-26.3305</v>
       </c>
       <c r="H14" t="n">
-        <v>-3.0592</v>
+        <v>-31.9361</v>
       </c>
       <c r="I14" t="n">
-        <v>-9.5952</v>
+        <v>5.605699999999999</v>
       </c>
       <c r="J14" t="n">
-        <v>-6.9875</v>
+        <v>32.50160000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>0.3797</v>
+        <v>16.834</v>
       </c>
       <c r="L14" t="n">
-        <v>-7.3672</v>
+        <v>15.6677</v>
       </c>
       <c r="M14" t="n">
-        <v>-5.667</v>
+        <v>-58.8325</v>
       </c>
       <c r="N14" t="n">
-        <v>-3.4389</v>
+        <v>-48.7704</v>
       </c>
       <c r="O14" t="n">
-        <v>-2.228</v>
+        <v>-10.0617</v>
       </c>
       <c r="P14" t="n">
-        <v>1.6437</v>
+        <v>2.054500000000001</v>
       </c>
       <c r="Q14" t="n">
-        <v>-3.0822</v>
+        <v>-60.61680000000001</v>
       </c>
       <c r="R14" t="n">
-        <v>4.726</v>
+        <v>62.6716</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.8024</v>
+        <v>-14.2358</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.0098</v>
+        <v>-10.9856</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.7927</v>
+        <v>-3.2507</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.1781</v>
+        <v>-14.137</v>
       </c>
       <c r="W14" t="n">
-        <v>1.4178</v>
+        <v>10.5959</v>
       </c>
       <c r="X14" t="n">
-        <v>-2.5959</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>--- TOTAL ---</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>SOL GIRONÈS BISBAL BÀSQUET</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>4</v>
-      </c>
-      <c r="D15" t="n">
-        <v>-52.649</v>
-      </c>
-      <c r="E15" t="n">
-        <v>-28.5053</v>
-      </c>
-      <c r="F15" t="n">
-        <v>-24.1436</v>
-      </c>
-      <c r="G15" t="n">
-        <v>-26.3305</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-31.936</v>
-      </c>
-      <c r="I15" t="n">
-        <v>5.605800000000002</v>
-      </c>
-      <c r="J15" t="n">
-        <v>32.50160000000001</v>
-      </c>
-      <c r="K15" t="n">
-        <v>16.834</v>
-      </c>
-      <c r="L15" t="n">
-        <v>15.6677</v>
-      </c>
-      <c r="M15" t="n">
-        <v>-58.8325</v>
-      </c>
-      <c r="N15" t="n">
-        <v>-48.7704</v>
-      </c>
-      <c r="O15" t="n">
-        <v>-10.0617</v>
-      </c>
-      <c r="P15" t="n">
-        <v>2.054500000000001</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>-60.61680000000001</v>
-      </c>
-      <c r="R15" t="n">
-        <v>62.6716</v>
-      </c>
-      <c r="S15" t="n">
-        <v>-14.2358</v>
-      </c>
-      <c r="T15" t="n">
-        <v>-10.9856</v>
-      </c>
-      <c r="U15" t="n">
-        <v>-3.2507</v>
-      </c>
-      <c r="V15" t="n">
-        <v>-14.137</v>
-      </c>
-      <c r="W15" t="n">
-        <v>10.5959</v>
-      </c>
-      <c r="X15" t="n">
         <v>-24.7326</v>
       </c>
     </row>
